--- a/assets/r04/sheets/空白NPC角色卡.xlsx
+++ b/assets/r04/sheets/空白NPC角色卡.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="空白NPC角色卡" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -26,18 +26,27 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Microsoft JhengHei"/>
       <b val="1"/>
-      <color rgb="002B5797"/>
-      <sz val="14"/>
+      <sz val="16"/>
     </font>
     <font>
+      <name val="Microsoft JhengHei"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft JhengHei"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
       <sz val="12"/>
     </font>
     <font>
+      <name val="Microsoft JhengHei"/>
       <b val="1"/>
-      <sz val="11"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft JhengHei"/>
+      <sz val="9"/>
     </font>
   </fonts>
   <fills count="4">
@@ -49,16 +58,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="002B5797"/>
+        <fgColor rgb="00D9E2F3"/>
+        <bgColor rgb="00D9E2F3"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
+        <bgColor rgb="00F2F2F2"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -67,74 +78,116 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="00BBBBBB"/>
-      </left>
-      <right style="thin">
-        <color rgb="00BBBBBB"/>
-      </right>
-      <top style="thin">
-        <color rgb="00BBBBBB"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00BBBBBB"/>
-      </bottom>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="00BBBBBB"/>
-      </left>
+      <left/>
+      <right/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin"/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="00BBBBBB"/>
-      </left>
-      <right style="thin">
-        <color rgb="00BBBBBB"/>
-      </right>
+      <left/>
+      <right style="thin"/>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="00BBBBBB"/>
-      </left>
-      <right style="thin">
-        <color rgb="00BBBBBB"/>
-      </right>
+      <left style="thin"/>
+      <right/>
       <top/>
-      <bottom style="thin">
-        <color rgb="00BBBBBB"/>
-      </bottom>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top/>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -497,153 +550,458 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="0070AD47"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B20"/>
+  <dimension ref="A1:F42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>空白NPC角色卡</t>
-        </is>
-      </c>
-    </row>
+          <t>凍結廢土 TRPG — NPC角色卡</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>欄位</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>內容</t>
-        </is>
-      </c>
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>基本資訊</t>
+        </is>
+      </c>
+      <c r="B3" s="10" t="n"/>
+      <c r="C3" s="10" t="n"/>
+      <c r="D3" s="10" t="n"/>
+      <c r="E3" s="10" t="n"/>
+      <c r="F3" s="11" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>編號</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr"/>
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>NPC姓名</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr"/>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>身份/職業</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr"/>
+      <c r="E4" s="6" t="inlineStr"/>
+      <c r="F4" s="6" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>名稱</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr"/>
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>所屬陣營</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr"/>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>所在聚居地</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr"/>
+      <c r="E5" s="6" t="inlineStr"/>
+      <c r="F5" s="6" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>等級/身分</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>魅力</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr"/>
-    </row>
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>動機/目標</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr"/>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>對掠奪者態度</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr"/>
+      <c r="E6" s="6" t="inlineStr"/>
+      <c r="F6" s="6" t="inlineStr"/>
+    </row>
+    <row r="7"/>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>智力</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr"/>
+          <t>描述</t>
+        </is>
+      </c>
+      <c r="B8" s="10" t="n"/>
+      <c r="C8" s="10" t="n"/>
+      <c r="D8" s="10" t="n"/>
+      <c r="E8" s="10" t="n"/>
+      <c r="F8" s="11" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>體力</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr"/>
+      <c r="A9" s="7" t="inlineStr"/>
+      <c r="B9" s="12" t="n"/>
+      <c r="C9" s="12" t="n"/>
+      <c r="D9" s="12" t="n"/>
+      <c r="E9" s="12" t="n"/>
+      <c r="F9" s="13" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>咒力</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr"/>
+      <c r="A10" s="14" t="n"/>
+      <c r="F10" s="15" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>心力</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>核心能力</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="inlineStr"/>
-    </row>
+      <c r="A11" s="16" t="n"/>
+      <c r="B11" s="17" t="n"/>
+      <c r="C11" s="17" t="n"/>
+      <c r="D11" s="17" t="n"/>
+      <c r="E11" s="17" t="n"/>
+      <c r="F11" s="18" t="n"/>
+    </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>標籤</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="inlineStr"/>
+          <t>五大屬性</t>
+        </is>
+      </c>
+      <c r="B13" s="10" t="n"/>
+      <c r="C13" s="10" t="n"/>
+      <c r="D13" s="10" t="n"/>
+      <c r="E13" s="10" t="n"/>
+      <c r="F13" s="11" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>背景</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="inlineStr"/>
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>屬性</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>值 (1–10)</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>修正值</t>
+        </is>
+      </c>
+      <c r="D14" s="8" t="inlineStr">
+        <is>
+          <t>說明</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>角色圖</t>
-        </is>
-      </c>
-      <c r="B15" s="6" t="inlineStr">
-        <is>
-          <t>【在此貼上角色圖片】</t>
-        </is>
-      </c>
+          <t>速度（SPD）</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr"/>
+      <c r="C15" s="6">
+        <f>B15-5</f>
+        <v/>
+      </c>
+      <c r="D15" s="9" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="B16" s="7" t="n"/>
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>知覺（PER）</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr"/>
+      <c r="C16" s="6">
+        <f>B16-5</f>
+        <v/>
+      </c>
+      <c r="D16" s="9" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="B17" s="7" t="n"/>
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>膽量（GUT）</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr"/>
+      <c r="C17" s="6">
+        <f>B17-5</f>
+        <v/>
+      </c>
+      <c r="D17" s="9" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="B18" s="7" t="n"/>
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>技術（TEC）</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="inlineStr"/>
+      <c r="C18" s="6">
+        <f>B18-5</f>
+        <v/>
+      </c>
+      <c r="D18" s="9" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="B19" s="7" t="n"/>
-    </row>
-    <row r="20">
-      <c r="B20" s="8" t="n"/>
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>交涉（NEG）</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="inlineStr"/>
+      <c r="C19" s="6">
+        <f>B19-5</f>
+        <v/>
+      </c>
+      <c r="D19" s="9" t="inlineStr"/>
+    </row>
+    <row r="20"/>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>衍生屬性</t>
+        </is>
+      </c>
+      <c r="B21" s="10" t="n"/>
+      <c r="C21" s="10" t="n"/>
+      <c r="D21" s="10" t="n"/>
+      <c r="E21" s="10" t="n"/>
+      <c r="F21" s="11" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>生命值（HP）</t>
+        </is>
+      </c>
+      <c r="B22" s="6">
+        <f>B17*2+10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>防禦值（AC） (迴避難度)</t>
+        </is>
+      </c>
+      <c r="B23" s="6">
+        <f>10+B15-5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>移動力</t>
+        </is>
+      </c>
+      <c r="B24" s="6">
+        <f>B15+3</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>恐慌閾值</t>
+        </is>
+      </c>
+      <c r="B25" s="6">
+        <f>B17*2+5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>先攻修正</t>
+        </is>
+      </c>
+      <c r="B26" s="6">
+        <f>B15-5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27"/>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>裝備與資源</t>
+        </is>
+      </c>
+      <c r="B28" s="10" t="n"/>
+      <c r="C28" s="10" t="n"/>
+      <c r="D28" s="10" t="n"/>
+      <c r="E28" s="10" t="n"/>
+      <c r="F28" s="11" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>護甲 (名稱/防護值)</t>
+        </is>
+      </c>
+      <c r="B29" s="7" t="inlineStr"/>
+      <c r="C29" s="10" t="n"/>
+      <c r="D29" s="10" t="n"/>
+      <c r="E29" s="10" t="n"/>
+      <c r="F29" s="11" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>武器 1 (名稱/傷害/射程)</t>
+        </is>
+      </c>
+      <c r="B30" s="7" t="inlineStr"/>
+      <c r="C30" s="10" t="n"/>
+      <c r="D30" s="10" t="n"/>
+      <c r="E30" s="10" t="n"/>
+      <c r="F30" s="11" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>武器 2</t>
+        </is>
+      </c>
+      <c r="B31" s="7" t="inlineStr"/>
+      <c r="C31" s="10" t="n"/>
+      <c r="D31" s="10" t="n"/>
+      <c r="E31" s="10" t="n"/>
+      <c r="F31" s="11" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>特殊道具</t>
+        </is>
+      </c>
+      <c r="B32" s="7" t="inlineStr"/>
+      <c r="C32" s="10" t="n"/>
+      <c r="D32" s="10" t="n"/>
+      <c r="E32" s="10" t="n"/>
+      <c r="F32" s="11" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>時間結晶 (顆)</t>
+        </is>
+      </c>
+      <c r="B33" s="7" t="inlineStr"/>
+      <c r="C33" s="10" t="n"/>
+      <c r="D33" s="10" t="n"/>
+      <c r="E33" s="10" t="n"/>
+      <c r="F33" s="11" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>廢鐵幣</t>
+        </is>
+      </c>
+      <c r="B34" s="7" t="inlineStr"/>
+      <c r="C34" s="10" t="n"/>
+      <c r="D34" s="10" t="n"/>
+      <c r="E34" s="10" t="n"/>
+      <c r="F34" s="11" t="n"/>
+    </row>
+    <row r="35"/>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>行為模式 / 角色備註</t>
+        </is>
+      </c>
+      <c r="B36" s="10" t="n"/>
+      <c r="C36" s="10" t="n"/>
+      <c r="D36" s="10" t="n"/>
+      <c r="E36" s="10" t="n"/>
+      <c r="F36" s="11" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="9" t="inlineStr"/>
+      <c r="B37" s="10" t="n"/>
+      <c r="C37" s="10" t="n"/>
+      <c r="D37" s="10" t="n"/>
+      <c r="E37" s="10" t="n"/>
+      <c r="F37" s="11" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="9" t="inlineStr"/>
+      <c r="B38" s="10" t="n"/>
+      <c r="C38" s="10" t="n"/>
+      <c r="D38" s="10" t="n"/>
+      <c r="E38" s="10" t="n"/>
+      <c r="F38" s="11" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="9" t="inlineStr"/>
+      <c r="B39" s="10" t="n"/>
+      <c r="C39" s="10" t="n"/>
+      <c r="D39" s="10" t="n"/>
+      <c r="E39" s="10" t="n"/>
+      <c r="F39" s="11" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="9" t="inlineStr"/>
+      <c r="B40" s="10" t="n"/>
+      <c r="C40" s="10" t="n"/>
+      <c r="D40" s="10" t="n"/>
+      <c r="E40" s="10" t="n"/>
+      <c r="F40" s="11" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="9" t="inlineStr"/>
+      <c r="B41" s="10" t="n"/>
+      <c r="C41" s="10" t="n"/>
+      <c r="D41" s="10" t="n"/>
+      <c r="E41" s="10" t="n"/>
+      <c r="F41" s="11" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="9" t="inlineStr"/>
+      <c r="B42" s="10" t="n"/>
+      <c r="C42" s="10" t="n"/>
+      <c r="D42" s="10" t="n"/>
+      <c r="E42" s="10" t="n"/>
+      <c r="F42" s="11" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="B15:B20"/>
+  <mergeCells count="20">
+    <mergeCell ref="A41:F41"/>
+    <mergeCell ref="A37:F37"/>
+    <mergeCell ref="B31:F31"/>
+    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="A21:F21"/>
+    <mergeCell ref="A42:F42"/>
+    <mergeCell ref="A8:F8"/>
+    <mergeCell ref="A38:F38"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="A28:F28"/>
+    <mergeCell ref="A13:F13"/>
+    <mergeCell ref="B34:F34"/>
+    <mergeCell ref="A40:F40"/>
+    <mergeCell ref="A39:F39"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="A36:F36"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="A9:F11"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="B32:F32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
